--- a/planilha_padrao_original.xlsx
+++ b/planilha_padrao_original.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{265966BC-ABAA-094B-9F7F-F747E29CF3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="16">
   <si>
     <r>
       <rPr>
@@ -91,120 +91,6 @@
   </si>
   <si>
     <t>Valor Unitário</t>
-  </si>
-  <si>
-    <t>SUCO POMARIS LARANJA INTEG PET 1,5L</t>
-  </si>
-  <si>
-    <t>SUCO POMARIS LARANJA PET 900ML</t>
-  </si>
-  <si>
-    <t>SUCO POMARIS LARANJA INTEG 300ML</t>
-  </si>
-  <si>
-    <t>MANTEIGA GALBANI EXT C/SAL TAB 200G</t>
-  </si>
-  <si>
-    <t>QUEIJO GODAM MINAS FRESCAL LIGHT KG</t>
-  </si>
-  <si>
-    <t>QUEIJO GODAM MINAS PADRAO S/LACT KG</t>
-  </si>
-  <si>
-    <t>QUEIJO GODAM MINAS FRESCAL POTE KG</t>
-  </si>
-  <si>
-    <t>QUEIJO TIROLEZ COTTAGE POTE 200G</t>
-  </si>
-  <si>
-    <t>MANTEIGA FRIMESA S/SAL PT 200G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANTEIGA SERRAMAR C/SAL PT 200G </t>
-  </si>
-  <si>
-    <t>REQUEIJAO SERRAMAR CREMOSO CP 180G</t>
-  </si>
-  <si>
-    <t>REQUEIJAO POCOS CALDAS TRAD CP 200G</t>
-  </si>
-  <si>
-    <t>REQUEIJAO GALBANI CREM TRAD PT 380G</t>
-  </si>
-  <si>
-    <t>CREME GALBANI RICOTA 200G</t>
-  </si>
-  <si>
-    <t>CREME QUATA RICOTA 250G</t>
-  </si>
-  <si>
-    <t>CREME GODAM RICOTA 180G TRAD</t>
-  </si>
-  <si>
-    <t>CREME GODAM RICOTA 180G LIGHT P PERU</t>
-  </si>
-  <si>
-    <t>REQUEIJAO PEDRA SELADA CREMOSO 200G</t>
-  </si>
-  <si>
-    <t>REQUEIJAO VIGOR LIGHT 200G</t>
-  </si>
-  <si>
-    <t>REQUEIJAO FRIMESA TRAD CP 200G</t>
-  </si>
-  <si>
-    <t>QUEIJO FRIMESA COLONIAL KG</t>
-  </si>
-  <si>
-    <t>BANHA FRIMESA POTE 450G</t>
-  </si>
-  <si>
-    <t>6 und</t>
-  </si>
-  <si>
-    <t>7 und</t>
-  </si>
-  <si>
-    <t>12 und</t>
-  </si>
-  <si>
-    <t>22 und</t>
-  </si>
-  <si>
-    <t>5 und</t>
-  </si>
-  <si>
-    <t>10 und</t>
-  </si>
-  <si>
-    <t>36 und</t>
-  </si>
-  <si>
-    <t>87 und</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 und </t>
-  </si>
-  <si>
-    <t>33 und</t>
-  </si>
-  <si>
-    <t>14 und</t>
-  </si>
-  <si>
-    <t>50 und</t>
-  </si>
-  <si>
-    <t>89 und</t>
-  </si>
-  <si>
-    <t>4 und</t>
-  </si>
-  <si>
-    <t>27 und</t>
-  </si>
-  <si>
-    <t>24 und</t>
   </si>
 </sst>
 </file>
@@ -466,24 +352,6 @@
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -526,11 +394,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -910,7 +796,7 @@
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.9765625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="4.9765625" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.10546875" customWidth="1"/>
     <col min="3" max="3" width="11.1640625" customWidth="1"/>
     <col min="4" max="4" width="16.6796875" customWidth="1"/>
@@ -921,729 +807,558 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8"/>
-      <c r="B1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="10" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="13" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14"/>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="14"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="26"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="23">
+      <c r="A7" s="17">
         <v>1</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="16">
-        <v>7898748420432</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="17">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="17">
+        <v>3</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="17">
+        <v>4</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="17">
+        <v>5</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="17">
+        <v>6</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="17">
+        <v>7</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="17">
+        <v>8</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="17">
+        <v>9</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="17">
+        <v>10</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="17">
+        <v>11</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="17">
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="17">
         <v>13</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="19">
-        <v>46067</v>
-      </c>
-      <c r="I7" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="23">
-        <v>2</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16">
-        <v>7898962571705</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="17">
         <v>14</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="19">
-        <v>46067</v>
-      </c>
-      <c r="I8" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="23">
-        <v>3</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16">
-        <v>7898047190227</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="17">
         <v>15</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="19">
-        <v>46065</v>
-      </c>
-      <c r="I9" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="23">
-        <v>4</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16">
-        <v>7891097105920</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="17">
         <v>16</v>
       </c>
-      <c r="F10" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="19">
-        <v>46027</v>
-      </c>
-      <c r="I10" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="23">
-        <v>5</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16">
-        <v>8924</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="17">
         <v>17</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="19">
-        <v>46043</v>
-      </c>
-      <c r="I11" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="23">
-        <v>6</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16">
-        <v>6068</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="17">
         <v>18</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="19">
-        <v>46045</v>
-      </c>
-      <c r="I12" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="23">
-        <v>7</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16">
-        <v>5655</v>
-      </c>
-      <c r="E13" s="17" t="s">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="17">
         <v>19</v>
       </c>
-      <c r="F13" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="21"/>
-      <c r="H13" s="19">
-        <v>46043</v>
-      </c>
-      <c r="I13" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="23">
-        <v>8</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16">
-        <v>7896030519826</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="17">
         <v>20</v>
       </c>
-      <c r="F14" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="19">
-        <v>46032</v>
-      </c>
-      <c r="I14" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="23">
-        <v>9</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16">
-        <v>7896275981952</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="17">
         <v>21</v>
       </c>
-      <c r="F15" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="19">
-        <v>46071</v>
-      </c>
-      <c r="I15" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="23">
-        <v>10</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16">
-        <v>7897951610623</v>
-      </c>
-      <c r="E16" s="17" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="18">
         <v>22</v>
       </c>
-      <c r="F16" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="19">
-        <v>46042</v>
-      </c>
-      <c r="I16" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="23">
-        <v>11</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="16">
-        <v>7897951610432</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="18">
         <v>23</v>
       </c>
-      <c r="F17" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="19">
-        <v>46049</v>
-      </c>
-      <c r="I17" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="23">
-        <v>12</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16">
-        <v>7898955617397</v>
-      </c>
-      <c r="E18" s="17" t="s">
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="18">
         <v>24</v>
       </c>
-      <c r="F18" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="19">
-        <v>46050</v>
-      </c>
-      <c r="I18" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="23">
-        <v>13</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16">
-        <v>7891097107238</v>
-      </c>
-      <c r="E19" s="17" t="s">
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="18">
         <v>25</v>
       </c>
-      <c r="F19" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="19">
-        <v>46050</v>
-      </c>
-      <c r="I19" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="23">
-        <v>14</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16">
-        <v>7891097105975</v>
-      </c>
-      <c r="E20" s="17" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="18">
         <v>26</v>
       </c>
-      <c r="F20" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="19">
-        <v>46051</v>
-      </c>
-      <c r="I20" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="23">
-        <v>15</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16">
-        <v>7896183202200</v>
-      </c>
-      <c r="E21" s="17" t="s">
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="17">
         <v>27</v>
       </c>
-      <c r="F21" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="19">
-        <v>46051</v>
-      </c>
-      <c r="I21" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="23">
-        <v>16</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16">
-        <v>7898227281318</v>
-      </c>
-      <c r="E22" s="17" t="s">
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="17">
         <v>28</v>
       </c>
-      <c r="F22" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="19">
-        <v>46030</v>
-      </c>
-      <c r="I22" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="23">
-        <v>17</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="16">
-        <v>7898227281349</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="17">
         <v>29</v>
       </c>
-      <c r="F23" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="19">
-        <v>46047</v>
-      </c>
-      <c r="I23" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="23">
-        <v>18</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16">
-        <v>78930599</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" s="17">
         <v>30</v>
       </c>
-      <c r="F24" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="19">
-        <v>46054</v>
-      </c>
-      <c r="I24" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="23">
-        <v>19</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16">
-        <v>7891999144461</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="19">
-        <v>46042</v>
-      </c>
-      <c r="I25" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="23">
-        <v>20</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="16">
-        <v>7896275960193</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="19">
-        <v>46048</v>
-      </c>
-      <c r="I26" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="23">
-        <v>21</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="16">
-        <v>6501</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="19">
-        <v>46056</v>
-      </c>
-      <c r="I27" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="24">
-        <v>22</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16">
-        <v>7896275921101</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="19">
-        <v>46079</v>
-      </c>
-      <c r="I28" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="24">
-        <v>23</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="24">
-        <v>24</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="24">
-        <v>25</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="24">
-        <v>26</v>
-      </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="23">
-        <v>27</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="23">
-        <v>28</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="23">
-        <v>29</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="23">
-        <v>30</v>
-      </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="20">
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="14">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:D4"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="I5:I6"/>
@@ -1652,13 +1367,8 @@
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B1:D4"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H36 H7:H28">
+  <conditionalFormatting sqref="H7:H28 H36">
     <cfRule type="expression" dxfId="4" priority="2">
       <formula>AND(H7&lt;&gt;"",H7&lt;TODAY())</formula>
     </cfRule>
